--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488092_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488092_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2529</v>
+        <v>6.2025</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9866</v>
+        <v>3.8613</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2663</v>
+        <v>2.3412</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6256</v>
+        <v>-0.6015</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3495</v>
+        <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2761</v>
+        <v>-0.7919</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3076</v>
+        <v>0.212</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7334</v>
+        <v>0.908</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5742</v>
+        <v>-0.696</v>
       </c>
       <c r="M2" t="n">
-        <v>0.318</v>
+        <v>-0.8135</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3839</v>
+        <v>-0.7176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7019</v>
+        <v>-0.0959</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>1.343</v>
+        <v>-0.2753</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4844</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8273</v>
+        <v>0.5669</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8701</v>
+        <v>4.8988</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1367</v>
+        <v>4.4914</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2666</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. RUBIO MIRAS</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8335</v>
+        <v>4.6881</v>
       </c>
       <c r="E3" t="n">
-        <v>3.431</v>
+        <v>2.2922</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4025</v>
+        <v>2.3959</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1417</v>
+        <v>4.6256</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8008</v>
+        <v>3.3495</v>
       </c>
       <c r="I3" t="n">
-        <v>5.9424</v>
+        <v>1.2761</v>
       </c>
       <c r="J3" t="n">
-        <v>6.4304</v>
+        <v>4.3076</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7938</v>
+        <v>3.7334</v>
       </c>
       <c r="L3" t="n">
-        <v>5.6365</v>
+        <v>0.5742</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2887</v>
+        <v>0.318</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5946</v>
+        <v>-0.3839</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3059</v>
+        <v>0.7019</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.9822</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.467</v>
+        <v>0.7782</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.242</v>
+        <v>-0.1787</v>
       </c>
       <c r="U3" t="n">
-        <v>0.709</v>
+        <v>0.9569</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>0.8701</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>D. RUBIO MIRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7907</v>
+        <v>4.6859</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8426</v>
+        <v>3.2273</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9481</v>
+        <v>1.4586</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6015</v>
+        <v>5.1417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1904</v>
+        <v>-0.8008</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7919</v>
+        <v>5.9424</v>
       </c>
       <c r="J4" t="n">
-        <v>0.212</v>
+        <v>6.4304</v>
       </c>
       <c r="K4" t="n">
-        <v>0.908</v>
+        <v>0.7938</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.696</v>
+        <v>5.6365</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8135</v>
+        <v>-1.2887</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7176</v>
+        <v>-1.5946</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0959</v>
+        <v>0.3059</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6871</v>
+        <v>0.3194</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.8609</v>
+        <v>-0.4457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1738</v>
+        <v>0.7651</v>
       </c>
       <c r="V4" t="n">
-        <v>4.8988</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>4.4914</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBINO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9844</v>
+        <v>2.3604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6764</v>
+        <v>1.5614</v>
       </c>
       <c r="F5" t="n">
-        <v>2.308</v>
+        <v>0.799</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3477</v>
+        <v>1.2311</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5852000000000001</v>
+        <v>1.0896</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2374</v>
+        <v>0.1415</v>
       </c>
       <c r="J5" t="n">
-        <v>1.228</v>
+        <v>1.342</v>
       </c>
       <c r="K5" t="n">
-        <v>1.285</v>
+        <v>1.2176</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.057</v>
+        <v>0.1244</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5757</v>
+        <v>-0.1109</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8702</v>
+        <v>-0.128</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2945</v>
+        <v>0.0171</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9664</v>
+        <v>0.6029</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0034</v>
+        <v>0.2194</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9699</v>
+        <v>0.3835</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8148</v>
+        <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.5482</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.905</v>
+        <v>2.1107</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2745</v>
+        <v>2.1107</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6304999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2311</v>
+        <v>2.1107</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0896</v>
+        <v>0.3027</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1415</v>
+        <v>1.808</v>
       </c>
       <c r="J6" t="n">
-        <v>1.342</v>
+        <v>2.1107</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2176</v>
+        <v>0.3027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>1.808</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1109</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0171</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1476</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9325</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.215</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>A. CONTRERAS RUBINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1107</v>
+        <v>2.033</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1107</v>
+        <v>0.3707</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.6622</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1107</v>
+        <v>-0.3477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3027</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.808</v>
+        <v>0.2374</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1107</v>
+        <v>1.228</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3027</v>
+        <v>1.285</v>
       </c>
       <c r="L7" t="n">
-        <v>1.808</v>
+        <v>-0.057</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.5757</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.8702</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.2945</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.015</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.3091</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.324</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.8148</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.5482</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1233</v>
+        <v>-0.0672</v>
       </c>
       <c r="E8" t="n">
         <v>0.4383</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5617</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.8312</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4214</v>
+        <v>-0.3652</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5331</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>J. REVUELTAS PAREJA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3911</v>
+        <v>-1.725</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8541</v>
+        <v>-0.0036</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.537</v>
+        <v>-1.7214</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2943</v>
+        <v>0.1001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1541</v>
+        <v>-1.7175</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1403</v>
+        <v>1.8176</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.4462</v>
+        <v>0.2184</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2888</v>
+        <v>-0.9144</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1574</v>
+        <v>1.1328</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8481</v>
+        <v>-0.1184</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8652</v>
+        <v>-0.8032</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0171</v>
+        <v>0.6848</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2402</v>
+        <v>-0.0055</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0501</v>
+        <v>-0.222</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1901</v>
+        <v>0.2165</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.337</v>
+        <v>-2.4142</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8701</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. REVUELTAS PAREJA</t>
+          <t>F. GARCIA GARRIDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9287</v>
+        <v>-1.8454</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2073</v>
+        <v>-0.3504</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7214</v>
+        <v>-1.495</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1001</v>
+        <v>0.0587</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7175</v>
+        <v>-0.1575</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8176</v>
+        <v>0.2162</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2184</v>
+        <v>0.726</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9144</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1328</v>
+        <v>0.0804</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1184</v>
+        <v>-0.6674</v>
       </c>
       <c r="N10" t="n">
         <v>-0.8032</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6848</v>
+        <v>0.1358</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
         <v>0.5947</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2093</v>
+        <v>-0.034</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4257</v>
+        <v>-0.0853</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2165</v>
+        <v>0.0514</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4142</v>
+        <v>-1.4737</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.4142</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. GARCIA GARRIDO</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0596</v>
+        <v>-2.1852</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4523</v>
+        <v>-1.8728</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6073</v>
+        <v>-0.3124</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0587</v>
+        <v>-2.2943</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1575</v>
+        <v>-1.1541</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2162</v>
+        <v>-1.1403</v>
       </c>
       <c r="J11" t="n">
-        <v>0.726</v>
+        <v>-1.4462</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6457000000000001</v>
+        <v>-0.2888</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0804</v>
+        <v>-1.1574</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6674</v>
+        <v>-0.8481</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8032</v>
+        <v>-0.8652</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1358</v>
+        <v>0.0171</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2481</v>
+        <v>0.4461</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1872</v>
+        <v>0.0314</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0609</v>
+        <v>0.4147</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4737</v>
+        <v>-0.337</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4737</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7956</v>
+        <v>-3.6789</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.685</v>
+        <v>-5.0738</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8895</v>
+        <v>1.3949</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8288</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1937</v>
+        <v>-0.077</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0497</v>
+        <v>-0.4385</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.144</v>
+        <v>0.3615</v>
       </c>
       <c r="V12" t="n">
         <v>1.0109</v>
@@ -1426,16 +1426,16 @@
         <v>12.5789</v>
       </c>
       <c r="E13" t="n">
-        <v>6.561400000000002</v>
+        <v>6.561299999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>6.017500000000002</v>
+        <v>6.017499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>8.026800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6987000000000002</v>
+        <v>0.6986999999999991</v>
       </c>
       <c r="I13" t="n">
         <v>7.327900000000001</v>
@@ -1447,19 +1447,19 @@
         <v>8.3223</v>
       </c>
       <c r="L13" t="n">
-        <v>5.770100000000001</v>
+        <v>5.770099999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-6.0658</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.623700000000001</v>
+        <v>-7.623699999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1.5579</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0001999999999997559</v>
+        <v>0.0002000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.8933</v>
@@ -1474,13 +1474,13 @@
         <v>-2.4579</v>
       </c>
       <c r="U13" t="n">
-        <v>4.862499999999999</v>
+        <v>4.862400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>2.147499999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.820099999999999</v>
+        <v>6.820100000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-4.672599999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2118</v>
+        <v>7.4994</v>
       </c>
       <c r="E14" t="n">
-        <v>8.559900000000001</v>
+        <v>8.661799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3481</v>
+        <v>-1.1624</v>
       </c>
       <c r="G14" t="n">
         <v>6.2868</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4517</v>
+        <v>-0.2607</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1745</v>
+        <v>-1.0726</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6262</v>
+        <v>0.8119</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7072000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.77</v>
+        <v>2.1526</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0851</v>
+        <v>1.1869</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6849</v>
+        <v>0.9657</v>
       </c>
       <c r="G15" t="n">
         <v>1.0145</v>
@@ -1624,13 +1624,13 @@
         <v>0.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.4213</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4919</v>
+        <v>-0.2112</v>
       </c>
       <c r="V15" t="n">
         <v>0.7665</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VILLEGAS GIMENEZ</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2184</v>
+        <v>0.4488</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0202</v>
+        <v>0.6321</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1982</v>
+        <v>-0.1833</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0202</v>
+        <v>0.1374</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0202</v>
+        <v>0.1412</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.0039</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0202</v>
+        <v>1.0689</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0202</v>
+        <v>0.9484</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.9315</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.8071</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.1244</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.1092</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.4368</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.3276</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>D. VILLEGAS GIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1164</v>
+        <v>0.2184</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6321</v>
+        <v>0.0202</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5157</v>
+        <v>0.1982</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1374</v>
+        <v>0.0202</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1412</v>
+        <v>0.0202</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0039</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0689</v>
+        <v>0.0202</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9484</v>
+        <v>0.0202</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9315</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8071</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1244</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4416</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4368</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0048</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.174</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2855</v>
+        <v>-1.1275</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3822</v>
+        <v>-1.2803</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.1528</v>
       </c>
       <c r="G18" t="n">
         <v>-1.657</v>
@@ -1858,13 +1858,13 @@
         <v>0.5947</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2232</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3433</v>
+        <v>-1.2975</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2012</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8579</v>
+        <v>-0.4452</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6141</v>
+        <v>-3.1008</v>
       </c>
       <c r="H19" t="n">
-        <v>2.8195</v>
+        <v>-1.3426</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2053</v>
+        <v>-1.7582</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1325</v>
+        <v>-0.5836</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4907</v>
+        <v>0.128</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3583</v>
+        <v>-0.7115</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5184</v>
+        <v>-2.5172</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6713</v>
+        <v>-1.4705</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1529</v>
+        <v>-1.0467</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9733</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S19" t="n">
-        <v>0.886</v>
+        <v>0.614</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3047</v>
+        <v>-0.2687</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5813</v>
+        <v>0.8827</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.674</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6148</v>
+        <v>-1.6614</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.5317</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6607</v>
+        <v>-1.1297</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1008</v>
+        <v>-2.6598</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3426</v>
+        <v>-0.7426</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7582</v>
+        <v>-1.9171</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5836</v>
+        <v>-0.4388</v>
       </c>
       <c r="K20" t="n">
-        <v>0.128</v>
+        <v>-0.4906</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7115</v>
+        <v>0.0518</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5172</v>
+        <v>-2.221</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4705</v>
+        <v>-0.252</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0467</v>
+        <v>-1.969</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2966</v>
+        <v>-0.68</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3706</v>
+        <v>-0.8927</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6672</v>
+        <v>0.2127</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.0925</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7088</v>
+        <v>-2.0982</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.5068</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0752</v>
+        <v>0.4086</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6598</v>
+        <v>1.6141</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7426</v>
+        <v>2.8195</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9171</v>
+        <v>-1.2053</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4388</v>
+        <v>2.1325</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4906</v>
+        <v>3.4907</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0518</v>
+        <v>-1.3583</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.221</v>
+        <v>-0.5184</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.252</v>
+        <v>-0.6713</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.969</v>
+        <v>0.1529</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7274</v>
+        <v>0.1312</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9946</v>
+        <v>-0.0009</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7328</v>
+        <v>0.132</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0925</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7997</v>
+        <v>-0.674</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1388</v>
+        <v>-4.6011</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6636</v>
+        <v>-3.1729</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4752</v>
+        <v>-1.4282</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7718</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8927</v>
+        <v>0.4304</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0145</v>
+        <v>-0.5238</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9072</v>
+        <v>0.9542</v>
       </c>
       <c r="V22" t="n">
         <v>-0.0704</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.8444</v>
+        <v>-4.7931</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6173</v>
+        <v>-3.006</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2272</v>
+        <v>-1.787</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1869</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6093</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6113</v>
+        <v>-1.0001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.002</v>
+        <v>0.4421</v>
       </c>
       <c r="V23" t="n">
         <v>-1.8589</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9597</v>
+        <v>-5.961</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8628</v>
+        <v>-5.1685</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0969</v>
+        <v>-0.7926</v>
       </c>
       <c r="G24" t="n">
         <v>-4.7234</v>
@@ -2326,13 +2326,13 @@
         <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1262</v>
+        <v>-0.1276</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1282</v>
+        <v>-0.4339</v>
       </c>
       <c r="U24" t="n">
-        <v>0.002</v>
+        <v>0.3063</v>
       </c>
       <c r="V24" t="n">
         <v>0.674</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.5787</v>
+        <v>-11.2206</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.017499999999998</v>
+        <v>-6.0175</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.561299999999999</v>
+        <v>-5.2031</v>
       </c>
       <c r="G25" t="n">
         <v>-8.026699999999998</v>
@@ -2374,16 +2374,16 @@
         <v>-0.6987999999999996</v>
       </c>
       <c r="I25" t="n">
-        <v>-7.3278</v>
+        <v>-7.327799999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>6.065700000000001</v>
+        <v>6.065699999999999</v>
       </c>
       <c r="K25" t="n">
         <v>7.623599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.557900000000001</v>
+        <v>-1.5579</v>
       </c>
       <c r="M25" t="n">
         <v>-14.0925</v>
@@ -2404,13 +2404,13 @@
         <v>11.8934</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.404599999999999</v>
+        <v>-1.0464</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.8626</v>
+        <v>-4.862500000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>2.458</v>
+        <v>3.8161</v>
       </c>
       <c r="V25" t="n">
         <v>-2.1476</v>
